--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV23\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9D2991-3D22-43C1-8BAF-38FB59DFF9FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5AA439-8ACE-4773-ABF9-1953BA80AE35}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="65">
   <si>
     <t>S.No</t>
   </si>
@@ -188,6 +188,39 @@
   </si>
   <si>
     <t>Verify admin can add a new raw material successfully.</t>
+  </si>
+  <si>
+    <t>Product Stock</t>
+  </si>
+  <si>
+    <t>ProductStock</t>
+  </si>
+  <si>
+    <t>Verify that stock changes are reflected and saved successfully after adding stock.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PS_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PS_02</t>
+  </si>
+  <si>
+    <t>Verify that stock changes are reflected and saved successfully after adjusting stock.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_03</t>
+  </si>
+  <si>
+    <t>Verify that the low stock alert is saved and reflected successfully for the product.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PS_03</t>
   </si>
 </sst>
 </file>
@@ -361,7 +394,67 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -698,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -790,9 +883,120 @@
         <v>13</v>
       </c>
     </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:J4"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -802,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -1015,14 +1219,287 @@
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
     </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="1" priority="25" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="7" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="6" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
